--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488013_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488013_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.3515</v>
+        <v>4.3391</v>
       </c>
       <c r="E2" t="n">
-        <v>5.9266</v>
+        <v>4.9703</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.5750999999999999</v>
+        <v>-0.6312</v>
       </c>
       <c r="G2" t="n">
         <v>3.453</v>
@@ -610,13 +610,13 @@
         <v>2.1805</v>
       </c>
       <c r="S2" t="n">
-        <v>1.174</v>
+        <v>0.1615</v>
       </c>
       <c r="T2" t="n">
-        <v>1.351</v>
+        <v>0.3947</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1771</v>
+        <v>-0.2332</v>
       </c>
       <c r="V2" t="n">
         <v>-0.2666</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>E. KOYANOUBA DJIRANGAYE</t>
+          <t>C. BELEMENE DZABATOU</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.7366</v>
+        <v>1.7687</v>
       </c>
       <c r="E3" t="n">
-        <v>3.2328</v>
+        <v>3.6838</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.4961</v>
+        <v>-1.9151</v>
       </c>
       <c r="G3" t="n">
-        <v>-2.6236</v>
+        <v>4.9345</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.2938</v>
+        <v>1.4621</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.3298</v>
+        <v>3.4724</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.2382</v>
+        <v>6.9862</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.3626</v>
+        <v>1.9238</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1244</v>
+        <v>5.0624</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.3853</v>
+        <v>-2.0517</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.9312</v>
+        <v>-0.4617</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.4542</v>
+        <v>-1.59</v>
       </c>
       <c r="P3" t="n">
-        <v>0.5947</v>
+        <v>-2.1805</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1893</v>
+        <v>-3.9645</v>
       </c>
       <c r="R3" t="n">
         <v>1.784</v>
       </c>
       <c r="S3" t="n">
-        <v>1.1442</v>
+        <v>-0.3818</v>
       </c>
       <c r="T3" t="n">
-        <v>1.039</v>
+        <v>-0.545</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1052</v>
+        <v>0.1632</v>
       </c>
       <c r="V3" t="n">
-        <v>3.6213</v>
+        <v>-0.6036</v>
       </c>
       <c r="W3" t="n">
-        <v>3.6213</v>
+        <v>1.2071</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-1.8107</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>W. HASSAN</t>
+          <t>L. RUEDA SANTAELLA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.8616</v>
+        <v>1.6826</v>
       </c>
       <c r="E4" t="n">
-        <v>1.7021</v>
+        <v>5.1332</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1595</v>
+        <v>-3.4506</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3622</v>
+        <v>0.3471</v>
       </c>
       <c r="H4" t="n">
-        <v>2.503</v>
+        <v>-0.156</v>
       </c>
       <c r="I4" t="n">
-        <v>-2.1408</v>
+        <v>0.5031</v>
       </c>
       <c r="J4" t="n">
-        <v>2.1461</v>
+        <v>4.1884</v>
       </c>
       <c r="K4" t="n">
-        <v>2.0178</v>
+        <v>0.3638</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1283</v>
+        <v>3.8247</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.7839</v>
+        <v>-3.8413</v>
       </c>
       <c r="N4" t="n">
-        <v>0.4852</v>
+        <v>-0.5198</v>
       </c>
       <c r="O4" t="n">
-        <v>-2.2691</v>
+        <v>-3.3215</v>
       </c>
       <c r="P4" t="n">
-        <v>0.9911</v>
+        <v>2.5769</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.9911</v>
+        <v>-0.1982</v>
       </c>
       <c r="R4" t="n">
-        <v>1.9822</v>
+        <v>2.7751</v>
       </c>
       <c r="S4" t="n">
-        <v>1.3784</v>
+        <v>-1.171</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5471</v>
+        <v>-0.5973000000000001</v>
       </c>
       <c r="U4" t="n">
-        <v>0.8313</v>
+        <v>-0.5737</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.8701</v>
+        <v>-0.0704</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.7403</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.8701</v>
+        <v>-1.8107</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>C. BELEMENE DZABATOU</t>
+          <t>E. KOYANOUBA DJIRANGAYE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.7334</v>
+        <v>1.6191</v>
       </c>
       <c r="E5" t="n">
-        <v>3.4801</v>
+        <v>2.4802</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.7466</v>
+        <v>-0.8612</v>
       </c>
       <c r="G5" t="n">
-        <v>4.9345</v>
+        <v>-2.6236</v>
       </c>
       <c r="H5" t="n">
-        <v>1.4621</v>
+        <v>-1.2938</v>
       </c>
       <c r="I5" t="n">
-        <v>3.4724</v>
+        <v>-1.3298</v>
       </c>
       <c r="J5" t="n">
-        <v>6.9862</v>
+        <v>-0.2382</v>
       </c>
       <c r="K5" t="n">
-        <v>1.9238</v>
+        <v>-0.3626</v>
       </c>
       <c r="L5" t="n">
-        <v>5.0624</v>
+        <v>0.1244</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.0517</v>
+        <v>-2.3853</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.4617</v>
+        <v>-0.9312</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.59</v>
+        <v>-1.4542</v>
       </c>
       <c r="P5" t="n">
-        <v>-2.1805</v>
+        <v>0.5947</v>
       </c>
       <c r="Q5" t="n">
-        <v>-3.9645</v>
+        <v>-1.1893</v>
       </c>
       <c r="R5" t="n">
         <v>1.784</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.4171</v>
+        <v>0.0266</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.7488</v>
+        <v>0.2865</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3317</v>
+        <v>-0.2598</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.6036</v>
+        <v>3.6213</v>
       </c>
       <c r="W5" t="n">
-        <v>1.2071</v>
+        <v>3.6213</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.8107</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>L. RUEDA SANTAELLA</t>
+          <t>W. HASSAN</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6544</v>
+        <v>1.3137</v>
       </c>
       <c r="E6" t="n">
-        <v>4.3577</v>
+        <v>1.2946</v>
       </c>
       <c r="F6" t="n">
-        <v>-3.7033</v>
+        <v>0.0191</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3471</v>
+        <v>0.3622</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.156</v>
+        <v>2.503</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5031</v>
+        <v>-2.1408</v>
       </c>
       <c r="J6" t="n">
-        <v>4.1884</v>
+        <v>2.1461</v>
       </c>
       <c r="K6" t="n">
-        <v>0.3638</v>
+        <v>2.0178</v>
       </c>
       <c r="L6" t="n">
-        <v>3.8247</v>
+        <v>0.1283</v>
       </c>
       <c r="M6" t="n">
-        <v>-3.8413</v>
+        <v>-1.7839</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.5198</v>
+        <v>0.4852</v>
       </c>
       <c r="O6" t="n">
-        <v>-3.3215</v>
+        <v>-2.2691</v>
       </c>
       <c r="P6" t="n">
-        <v>2.5769</v>
+        <v>0.9911</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.1982</v>
+        <v>-0.9911</v>
       </c>
       <c r="R6" t="n">
-        <v>2.7751</v>
+        <v>1.9822</v>
       </c>
       <c r="S6" t="n">
-        <v>-2.1992</v>
+        <v>0.8306</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.3727</v>
+        <v>0.1396</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.8264</v>
+        <v>0.6909</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.0704</v>
+        <v>-0.8701</v>
       </c>
       <c r="W6" t="n">
-        <v>1.7403</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.8107</v>
+        <v>-0.8701</v>
       </c>
     </row>
     <row r="7">
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>P. BALLESTER MANQUE</t>
+          <t>R. CUBERO ROJANO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.4639</v>
+        <v>-1.264</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.9508</v>
+        <v>-0.0002</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.5132</v>
+        <v>-1.2638</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.4915</v>
+        <v>-1.9586</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0404</v>
+        <v>1.4164</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.5319</v>
+        <v>-3.3749</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0404</v>
+        <v>0.2952</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0404</v>
+        <v>0.7333</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>-0.4381</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.5319</v>
+        <v>-2.2538</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>0.6831</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.5319</v>
+        <v>-2.9369</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.9911</v>
+        <v>1.784</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9911</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.784</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0187</v>
+        <v>-0.2193</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>-0.2954</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0187</v>
+        <v>0.0761</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-0.8701</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.8701</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>R. CUBERO ROJANO</t>
+          <t>P. BALLESTER MANQUE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.7205</v>
+        <v>-1.334</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.2039</v>
+        <v>-0.8489</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.5165</v>
+        <v>-0.4851</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.9586</v>
+        <v>-0.4915</v>
       </c>
       <c r="H10" t="n">
-        <v>1.4164</v>
+        <v>0.0404</v>
       </c>
       <c r="I10" t="n">
-        <v>-3.3749</v>
+        <v>-0.5319</v>
       </c>
       <c r="J10" t="n">
-        <v>0.2952</v>
+        <v>0.0404</v>
       </c>
       <c r="K10" t="n">
-        <v>0.7333</v>
+        <v>0.0404</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.4381</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.2538</v>
+        <v>-0.5319</v>
       </c>
       <c r="N10" t="n">
-        <v>0.6831</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>-2.9369</v>
+        <v>-0.5319</v>
       </c>
       <c r="P10" t="n">
-        <v>1.784</v>
+        <v>-0.9911</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-0.9911</v>
       </c>
       <c r="R10" t="n">
-        <v>1.784</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.6758</v>
+        <v>0.1487</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4992</v>
+        <v>0.1019</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1766</v>
+        <v>0.0468</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.8701</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.8701</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.9291</v>
+        <v>-2.9851</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.7205</v>
+        <v>-0.945</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.2086</v>
+        <v>-2.0401</v>
       </c>
       <c r="G11" t="n">
         <v>-3.7361</v>
@@ -1312,13 +1312,13 @@
         <v>2.5769</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.7965</v>
+        <v>-0.8525</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.0608</v>
+        <v>-0.2853</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.7357</v>
+        <v>-0.5673</v>
       </c>
       <c r="V11" t="n">
         <v>1.2071</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.4824</v>
+        <v>-4.0863</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.8016</v>
+        <v>-1.4336</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.6808</v>
+        <v>-2.6527</v>
       </c>
       <c r="G12" t="n">
         <v>-3.8707</v>
@@ -1390,13 +1390,13 @@
         <v>2.9733</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.233</v>
+        <v>-0.8369</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6312</v>
+        <v>-0.2632</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.6018</v>
+        <v>-0.5737</v>
       </c>
       <c r="V12" t="n">
         <v>1.8107</v>
@@ -1423,19 +1423,19 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1.013199999999999</v>
+        <v>1.325400000000003</v>
       </c>
       <c r="E13" t="n">
-        <v>14.0225</v>
+        <v>14.3344</v>
       </c>
       <c r="F13" t="n">
         <v>-13.0091</v>
       </c>
       <c r="G13" t="n">
-        <v>-3.3121</v>
+        <v>-3.312100000000001</v>
       </c>
       <c r="H13" t="n">
-        <v>7.411700000000001</v>
+        <v>7.411700000000002</v>
       </c>
       <c r="I13" t="n">
         <v>-10.7237</v>
@@ -1444,7 +1444,7 @@
         <v>19.2047</v>
       </c>
       <c r="K13" t="n">
-        <v>8.6523</v>
+        <v>8.652299999999999</v>
       </c>
       <c r="L13" t="n">
         <v>10.5525</v>
@@ -1459,7 +1459,7 @@
         <v>-21.276</v>
       </c>
       <c r="P13" t="n">
-        <v>2.9733</v>
+        <v>2.973300000000001</v>
       </c>
       <c r="Q13" t="n">
         <v>-14.8667</v>
@@ -1468,10 +1468,10 @@
         <v>17.84</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.6063</v>
+        <v>-2.2941</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.3756</v>
+        <v>-1.0635</v>
       </c>
       <c r="U13" t="n">
         <v>-1.2307</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>S. MELERO ZURITA</t>
+          <t>L. SIGISMONTI RODRIGUEZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.334</v>
+        <v>3.775</v>
       </c>
       <c r="E14" t="n">
-        <v>6.7002</v>
+        <v>3.539</v>
       </c>
       <c r="F14" t="n">
-        <v>-3.3661</v>
+        <v>0.236</v>
       </c>
       <c r="G14" t="n">
-        <v>2.678</v>
+        <v>2.4341</v>
       </c>
       <c r="H14" t="n">
-        <v>0.3725</v>
+        <v>0.4882</v>
       </c>
       <c r="I14" t="n">
-        <v>2.3054</v>
+        <v>1.9459</v>
       </c>
       <c r="J14" t="n">
-        <v>6.0686</v>
+        <v>4.7381</v>
       </c>
       <c r="K14" t="n">
-        <v>1.6413</v>
+        <v>0.9419999999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>4.4273</v>
+        <v>3.7962</v>
       </c>
       <c r="M14" t="n">
-        <v>-3.3907</v>
+        <v>-2.3041</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.2688</v>
+        <v>-0.4538</v>
       </c>
       <c r="O14" t="n">
-        <v>-2.1219</v>
+        <v>-1.8503</v>
       </c>
       <c r="P14" t="n">
-        <v>0.7929</v>
+        <v>0.3964</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.9911</v>
+        <v>-1.9822</v>
       </c>
       <c r="R14" t="n">
-        <v>1.784</v>
+        <v>2.3787</v>
       </c>
       <c r="S14" t="n">
-        <v>2.2774</v>
+        <v>0.0743</v>
       </c>
       <c r="T14" t="n">
-        <v>1.6227</v>
+        <v>-0.08699999999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>0.6546999999999999</v>
+        <v>0.1613</v>
       </c>
       <c r="V14" t="n">
-        <v>-2.4142</v>
+        <v>0.8701</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>0.8701</v>
       </c>
       <c r="X14" t="n">
-        <v>-2.4142</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>L. SIGISMONTI RODRIGUEZ</t>
+          <t>P. TRUÑO SOMS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.0619</v>
+        <v>3.0133</v>
       </c>
       <c r="E15" t="n">
-        <v>2.8259</v>
+        <v>3.0133</v>
       </c>
       <c r="F15" t="n">
-        <v>0.236</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>2.4341</v>
+        <v>3.0133</v>
       </c>
       <c r="H15" t="n">
-        <v>0.4882</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>1.9459</v>
+        <v>3.0133</v>
       </c>
       <c r="J15" t="n">
-        <v>4.7381</v>
+        <v>3.0133</v>
       </c>
       <c r="K15" t="n">
-        <v>0.9419999999999999</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>3.7962</v>
+        <v>3.0133</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.3041</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.4538</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.8503</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>0.3964</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.9822</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.3787</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.6388</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.8001</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1613</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>0.8701</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>0.8701</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>P. TRUÑO SOMS</t>
+          <t>S. MELERO ZURITA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.0133</v>
+        <v>2.2487</v>
       </c>
       <c r="E16" t="n">
-        <v>3.0133</v>
+        <v>5.7834</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>-3.5346</v>
       </c>
       <c r="G16" t="n">
-        <v>3.0133</v>
+        <v>2.678</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>0.3725</v>
       </c>
       <c r="I16" t="n">
-        <v>3.0133</v>
+        <v>2.3054</v>
       </c>
       <c r="J16" t="n">
-        <v>3.0133</v>
+        <v>6.0686</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>1.6413</v>
       </c>
       <c r="L16" t="n">
-        <v>3.0133</v>
+        <v>4.4273</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>-3.3907</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>-1.2688</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>-2.1219</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>0.7929</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-0.9911</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.784</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>1.1921</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>0.7058</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>0.4863</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>-2.4142</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-2.4142</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. JUZBASIC</t>
+          <t>J. VALEIRAS CREUS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.8525</v>
+        <v>0.5659</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.1216</v>
+        <v>4.9912</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9742</v>
+        <v>-4.4253</v>
       </c>
       <c r="G17" t="n">
-        <v>-2.3985</v>
+        <v>2.7667</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.3962</v>
+        <v>0.0118</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.0024</v>
+        <v>2.7549</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.9526</v>
+        <v>5.4743</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.0083</v>
+        <v>1.4124</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0557</v>
+        <v>4.0618</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.446</v>
+        <v>-2.7076</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.3879</v>
+        <v>-1.4007</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.0581</v>
+        <v>-1.3069</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.3964</v>
+        <v>1.3876</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.9822</v>
+        <v>-0.9911</v>
       </c>
       <c r="R17" t="n">
-        <v>1.5858</v>
+        <v>2.3787</v>
       </c>
       <c r="S17" t="n">
-        <v>0.6298</v>
+        <v>0.033</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.7377</v>
+        <v>0.2415</v>
       </c>
       <c r="U17" t="n">
-        <v>1.3675</v>
+        <v>-0.2085</v>
       </c>
       <c r="V17" t="n">
-        <v>3.0178</v>
+        <v>-3.6213</v>
       </c>
       <c r="W17" t="n">
-        <v>3.5509</v>
+        <v>0.2666</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.5331</v>
+        <v>-3.8879</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>P. ÁVALOS ORTIZ</t>
+          <t>D. JUZBASIC</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3027</v>
+        <v>0.4843</v>
       </c>
       <c r="E18" t="n">
-        <v>0.3027</v>
+        <v>0.184</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>0.3003</v>
       </c>
       <c r="G18" t="n">
-        <v>0.3027</v>
+        <v>-2.3985</v>
       </c>
       <c r="H18" t="n">
-        <v>0.3027</v>
+        <v>-1.3962</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>-1.0024</v>
       </c>
       <c r="J18" t="n">
-        <v>0.3027</v>
+        <v>-0.9526</v>
       </c>
       <c r="K18" t="n">
-        <v>0.3027</v>
+        <v>-1.0083</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>0.0557</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>-1.446</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>-0.3879</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>-1.0581</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>-0.3964</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-1.9822</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.5858</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>0.2615</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>-0.4321</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>0.6936</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>3.0178</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>3.5509</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.5331</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0003</v>
+        <v>0.4352</v>
       </c>
       <c r="E19" t="n">
-        <v>1.179</v>
+        <v>1.5864</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.1793</v>
+        <v>-1.1512</v>
       </c>
       <c r="G19" t="n">
         <v>-0.5580000000000001</v>
@@ -1936,13 +1936,13 @@
         <v>1.5858</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2529</v>
+        <v>0.1826</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3523</v>
+        <v>0.0552</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0994</v>
+        <v>0.1275</v>
       </c>
       <c r="V19" t="n">
         <v>1.2071</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. VALEIRAS CREUS</t>
+          <t>P. ÁVALOS ORTIZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.5475</v>
+        <v>0.3027</v>
       </c>
       <c r="E20" t="n">
-        <v>4.0744</v>
+        <v>0.3027</v>
       </c>
       <c r="F20" t="n">
-        <v>-4.6219</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>2.7667</v>
+        <v>0.3027</v>
       </c>
       <c r="H20" t="n">
-        <v>0.0118</v>
+        <v>0.3027</v>
       </c>
       <c r="I20" t="n">
-        <v>2.7549</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>5.4743</v>
+        <v>0.3027</v>
       </c>
       <c r="K20" t="n">
-        <v>1.4124</v>
+        <v>0.3027</v>
       </c>
       <c r="L20" t="n">
-        <v>4.0618</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.7076</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.4007</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.3069</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>1.3876</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9911</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.3787</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.0804</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6753</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.405</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>-3.6213</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>0.2666</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-3.8879</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>R. REVELLES DIAZ</t>
+          <t>M. BOTAS FERNANDEZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.0599</v>
+        <v>-1.4927</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.904</v>
+        <v>-1.6763</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.1559</v>
+        <v>0.1836</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.4899</v>
+        <v>1.4155</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.3101</v>
+        <v>-0.624</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.1799</v>
+        <v>2.0395</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.5584</v>
+        <v>2.5955</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.6388</v>
+        <v>-0.1003</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0804</v>
+        <v>2.6958</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.9315</v>
+        <v>-1.18</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.6713</v>
+        <v>-0.5237000000000001</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.2602</v>
+        <v>-0.6563</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.5858</v>
+        <v>-2.5769</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.9822</v>
+        <v>-3.9645</v>
       </c>
       <c r="R21" t="n">
-        <v>0.3964</v>
+        <v>1.3876</v>
       </c>
       <c r="S21" t="n">
-        <v>0.4123</v>
+        <v>-0.3313</v>
       </c>
       <c r="T21" t="n">
-        <v>0.4295</v>
+        <v>-0.3073</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0173</v>
+        <v>-0.024</v>
       </c>
       <c r="V21" t="n">
-        <v>0.6036</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.2071</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.6036</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>M. BOTAS FERNANDEZ</t>
+          <t>R. REVELLES DIAZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.1915</v>
+        <v>-2.2813</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.9819</v>
+        <v>-1.2096</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.2095</v>
+        <v>-1.0717</v>
       </c>
       <c r="G22" t="n">
-        <v>1.4155</v>
+        <v>-1.4899</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.624</v>
+        <v>-1.3101</v>
       </c>
       <c r="I22" t="n">
-        <v>2.0395</v>
+        <v>-0.1799</v>
       </c>
       <c r="J22" t="n">
-        <v>2.5955</v>
+        <v>-0.5584</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.1003</v>
+        <v>-0.6388</v>
       </c>
       <c r="L22" t="n">
-        <v>2.6958</v>
+        <v>0.0804</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.18</v>
+        <v>-0.9315</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.5237000000000001</v>
+        <v>-0.6713</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.6563</v>
+        <v>-0.2602</v>
       </c>
       <c r="P22" t="n">
-        <v>-2.5769</v>
+        <v>-1.5858</v>
       </c>
       <c r="Q22" t="n">
-        <v>-3.9645</v>
+        <v>-1.9822</v>
       </c>
       <c r="R22" t="n">
-        <v>1.3876</v>
+        <v>0.3964</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.03</v>
+        <v>0.1909</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6129</v>
+        <v>0.1239</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4171</v>
+        <v>0.067</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>0.6036</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.2071</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-0.6036</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>D. MELERO ZURITA</t>
+          <t>P. TRUNO SOMS</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.9872</v>
+        <v>-3.5774</v>
       </c>
       <c r="E23" t="n">
-        <v>0.5436</v>
+        <v>-2.5205</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.5307</v>
+        <v>-1.0569</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.2348</v>
+        <v>-3.6169</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.4572</v>
+        <v>-1.7648</v>
       </c>
       <c r="I23" t="n">
-        <v>1.2224</v>
+        <v>-1.8521</v>
       </c>
       <c r="J23" t="n">
-        <v>0.4846</v>
+        <v>-0.956</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.1225</v>
+        <v>-0.5581</v>
       </c>
       <c r="L23" t="n">
-        <v>1.6071</v>
+        <v>-0.3979</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.7194</v>
+        <v>-2.6609</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.3347</v>
+        <v>-1.2067</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.3847</v>
+        <v>-1.4542</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.1982</v>
+        <v>-0.3964</v>
       </c>
       <c r="Q23" t="n">
         <v>-1.9822</v>
       </c>
       <c r="R23" t="n">
-        <v>1.784</v>
+        <v>1.5858</v>
       </c>
       <c r="S23" t="n">
-        <v>2.0671</v>
+        <v>0.4359</v>
       </c>
       <c r="T23" t="n">
-        <v>2.0412</v>
+        <v>0.4176</v>
       </c>
       <c r="U23" t="n">
-        <v>0.026</v>
+        <v>0.0183</v>
       </c>
       <c r="V23" t="n">
-        <v>-3.6213</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-3.6213</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>P. TRUNO SOMS</t>
+          <t>D. MELERO ZURITA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.7916</v>
+        <v>-4.4871</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.6224</v>
+        <v>-0.9845</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.1692</v>
+        <v>-3.5027</v>
       </c>
       <c r="G24" t="n">
-        <v>-3.6169</v>
+        <v>-1.2348</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.7648</v>
+        <v>-2.4572</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.8521</v>
+        <v>1.2224</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.956</v>
+        <v>0.4846</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.5581</v>
+        <v>-1.1225</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.3979</v>
+        <v>1.6071</v>
       </c>
       <c r="M24" t="n">
-        <v>-2.6609</v>
+        <v>-1.7194</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.2067</v>
+        <v>-1.3347</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.4542</v>
+        <v>-0.3847</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.3964</v>
+        <v>-0.1982</v>
       </c>
       <c r="Q24" t="n">
         <v>-1.9822</v>
       </c>
       <c r="R24" t="n">
-        <v>1.5858</v>
+        <v>1.784</v>
       </c>
       <c r="S24" t="n">
-        <v>0.2217</v>
+        <v>0.5672</v>
       </c>
       <c r="T24" t="n">
-        <v>0.3158</v>
+        <v>0.5131</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.094</v>
+        <v>0.054</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>-3.6213</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>-3.6213</v>
       </c>
     </row>
     <row r="25">
@@ -2359,16 +2359,16 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-1.013599999999998</v>
+        <v>-1.0134</v>
       </c>
       <c r="E25" t="n">
-        <v>13.0092</v>
+        <v>13.0091</v>
       </c>
       <c r="F25" t="n">
-        <v>-14.0224</v>
+        <v>-14.0225</v>
       </c>
       <c r="G25" t="n">
-        <v>3.3122</v>
+        <v>3.312199999999999</v>
       </c>
       <c r="H25" t="n">
         <v>-7.4116</v>
@@ -2407,7 +2407,7 @@
         <v>2.6062</v>
       </c>
       <c r="T25" t="n">
-        <v>1.2309</v>
+        <v>1.2307</v>
       </c>
       <c r="U25" t="n">
         <v>1.3755</v>
